--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487854_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487854_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9791</v>
+        <v>3.3484</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6381</v>
+        <v>1.0715</v>
       </c>
       <c r="F2" t="n">
-        <v>1.341</v>
+        <v>2.277</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2699</v>
+        <v>3.27</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2558</v>
+        <v>2.6226</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0141</v>
+        <v>0.6474</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0823</v>
+        <v>1.4739</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4642</v>
+        <v>1.4347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.618</v>
+        <v>0.0392</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1876</v>
+        <v>1.7961</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2085</v>
+        <v>1.1879</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3961</v>
+        <v>0.6082</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1275</v>
+        <v>-0.754</v>
       </c>
       <c r="T2" t="n">
-        <v>1.304</v>
+        <v>-0.4024</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8235</v>
+        <v>-0.3516</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.0427</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9771</v>
+        <v>2.7934</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9643</v>
+        <v>2.2451</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0127</v>
+        <v>0.5483</v>
       </c>
       <c r="G3" t="n">
-        <v>3.27</v>
+        <v>5.2699</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6226</v>
+        <v>3.2558</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6474</v>
+        <v>2.0141</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4739</v>
+        <v>4.0823</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4347</v>
+        <v>3.4642</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0392</v>
+        <v>0.618</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7961</v>
+        <v>1.1876</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1879</v>
+        <v>-0.2085</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6082</v>
+        <v>1.3961</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1254</v>
+        <v>-0.0582</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.089</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6158</v>
+        <v>0.0308</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-3.0427</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1552</v>
+        <v>1.5204</v>
       </c>
       <c r="E4" t="n">
-        <v>1.999</v>
+        <v>3.0705</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8437</v>
+        <v>-1.5501</v>
       </c>
       <c r="G4" t="n">
         <v>2.1728</v>
@@ -766,13 +766,13 @@
         <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9383</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.162</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7763</v>
+        <v>-0.4827</v>
       </c>
       <c r="V4" t="n">
         <v>-1.7442</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6068</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3163</v>
+        <v>-0.9288</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9231</v>
+        <v>0.2238</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1829</v>
+        <v>0.1796</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8187</v>
+        <v>-0.3135</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3641</v>
+        <v>0.4931</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3418</v>
+        <v>-1.1307</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-1.1217</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7234</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8411</v>
+        <v>1.3104</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2003</v>
+        <v>0.8082</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3592</v>
+        <v>0.5021</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7842</v>
+        <v>-0.3634</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9068000000000001</v>
+        <v>-0.0281</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1226</v>
+        <v>-0.3353</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5838</v>
+        <v>-0.9376</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7513</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
         <v>-1.1675</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3686</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3575</v>
+        <v>0.8877</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0111</v>
+        <v>-1.7763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1796</v>
+        <v>-2.1829</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3135</v>
+        <v>-1.8187</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4931</v>
+        <v>-0.3641</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1307</v>
+        <v>-1.3418</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1217</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.7234</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3104</v>
+        <v>-0.8411</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8082</v>
+        <v>-1.2003</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5021</v>
+        <v>0.3592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0269</v>
+        <v>0.5023</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4567</v>
+        <v>0.4782</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5702</v>
+        <v>0.0242</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9376</v>
+        <v>0.5838</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>1.7513</v>
       </c>
       <c r="X6" t="n">
         <v>-1.1675</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6914</v>
+        <v>-2.5298</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1667</v>
+        <v>-2.1768</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3529</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1701</v>
+        <v>-0.6688</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1856</v>
+        <v>1.9976</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0155</v>
+        <v>-2.6664</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0514</v>
+        <v>-0.1664</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1689</v>
+        <v>2.8266</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1176</v>
+        <v>-2.993</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1187</v>
+        <v>-0.5024</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0167</v>
+        <v>-0.829</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.102</v>
+        <v>0.3266</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4162</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9492</v>
+        <v>-0.7036</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7358</v>
+        <v>-0.2862</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2134</v>
+        <v>-0.4175</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0543</v>
+        <v>-0.1168</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2843</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9202</v>
+        <v>-3.1406</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3912</v>
+        <v>-2.381</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5291</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6688</v>
+        <v>-2.1701</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9976</v>
+        <v>-2.1856</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6664</v>
+        <v>0.0155</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1664</v>
+        <v>-1.0514</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8266</v>
+        <v>-1.1689</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.993</v>
+        <v>0.1176</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5024</v>
+        <v>-1.1187</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.829</v>
+        <v>-1.0167</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3266</v>
+        <v>-0.102</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0941</v>
+        <v>0.5001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5004999999999999</v>
+        <v>0.5215</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5936</v>
+        <v>-0.0215</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1168</v>
+        <v>-1.0543</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5142</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.106</v>
+        <v>-3.3908</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0928</v>
+        <v>-4.8785</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9869</v>
+        <v>1.4878</v>
       </c>
       <c r="G9" t="n">
         <v>0.3707</v>
@@ -1156,13 +1156,13 @@
         <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.028</v>
+        <v>-0.3128</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3171</v>
+        <v>-0.1028</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2891</v>
+        <v>-0.21</v>
       </c>
       <c r="V9" t="n">
         <v>-1.9919</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3742</v>
+        <v>-4.9631</v>
       </c>
       <c r="E10" t="n">
         <v>-5.5911</v>
       </c>
       <c r="F10" t="n">
-        <v>0.217</v>
+        <v>0.628</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2605</v>
@@ -1234,13 +1234,13 @@
         <v>2.2893</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.77</v>
+        <v>-1.359</v>
       </c>
       <c r="T10" t="n">
         <v>-0.5004999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2695</v>
+        <v>-0.8585</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4706</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.955799999999998</v>
+        <v>-7.9558</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6816</v>
+        <v>-8.6814</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7259000000000001</v>
+        <v>0.7260000000000003</v>
       </c>
       <c r="G11" t="n">
         <v>4.980699999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9178000000000002</v>
+        <v>-0.9178000000000004</v>
       </c>
       <c r="I11" t="n">
         <v>5.898700000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9410000000000007</v>
+        <v>0.9410000000000012</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8141999999999998</v>
+        <v>-0.8141999999999996</v>
       </c>
       <c r="L11" t="n">
         <v>1.7553</v>
@@ -1297,7 +1297,7 @@
         <v>4.0398</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1036999999999999</v>
+        <v>-0.1037000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>4.1435</v>
@@ -1312,13 +1312,13 @@
         <v>12.4869</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.1218</v>
+        <v>-3.1217</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4997999999999997</v>
+        <v>-0.4996999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.622</v>
+        <v>-2.6221</v>
       </c>
       <c r="V11" t="n">
         <v>-8.774299999999998</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.370200000000001</v>
+        <v>6.5641</v>
       </c>
       <c r="E12" t="n">
-        <v>4.818</v>
+        <v>3.9575</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5522</v>
+        <v>2.6066</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9359</v>
+        <v>3.144</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2258</v>
+        <v>1.0279</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1618</v>
+        <v>2.1162</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8335</v>
+        <v>2.6911</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4385</v>
+        <v>0.8974</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.272</v>
+        <v>1.7937</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1024</v>
+        <v>0.4529</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2126</v>
+        <v>0.1304</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1102</v>
+        <v>0.3225</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>4.0553</v>
+        <v>0.4606</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3976</v>
+        <v>-0.0281</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6577</v>
+        <v>0.4887</v>
       </c>
       <c r="V12" t="n">
-        <v>4.2102</v>
+        <v>2.3351</v>
       </c>
       <c r="W12" t="n">
-        <v>3.5026</v>
+        <v>2.3351</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1394</v>
+        <v>6.3851</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5289</v>
+        <v>2.782</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6105</v>
+        <v>3.6031</v>
       </c>
       <c r="G13" t="n">
-        <v>3.144</v>
+        <v>-0.9359</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0279</v>
+        <v>0.2258</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1162</v>
+        <v>-1.1618</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6911</v>
+        <v>-0.8335</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8974</v>
+        <v>0.4385</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7937</v>
+        <v>-1.272</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4529</v>
+        <v>-0.1024</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1304</v>
+        <v>-0.2126</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3225</v>
+        <v>0.1102</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0359</v>
+        <v>2.0702</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4567</v>
+        <v>1.3616</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4926</v>
+        <v>0.7086</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3351</v>
+        <v>4.2102</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3351</v>
+        <v>3.5026</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1316</v>
+        <v>2.661</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8766</v>
+        <v>-0.6623</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0082</v>
+        <v>3.3233</v>
       </c>
       <c r="G14" t="n">
         <v>1.6063</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.2554</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3948</v>
+        <v>-0.1804</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3901</v>
+        <v>-0.075</v>
       </c>
       <c r="V14" t="n">
         <v>0.4776</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3035</v>
+        <v>0.0451</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5482</v>
+        <v>0.2908</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2447</v>
+        <v>-0.2457</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.451</v>
+        <v>2.1519</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0981</v>
+        <v>-0.4966</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3528</v>
+        <v>2.6485</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.8183</v>
+        <v>2.5072</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.4287</v>
+        <v>0.0384</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3896</v>
+        <v>2.4689</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3674</v>
+        <v>-0.3553</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3306</v>
+        <v>-0.5349</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0367</v>
+        <v>0.1796</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2081</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
         <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7718</v>
+        <v>-0.2337</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1025</v>
+        <v>-0.1352</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3308</v>
+        <v>-0.0985</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3644</v>
+        <v>-0.2065</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0306</v>
+        <v>0.2718</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3338</v>
+        <v>-0.4782</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1519</v>
+        <v>0.4456</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4966</v>
+        <v>-1.1129</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6485</v>
+        <v>1.5585</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5072</v>
+        <v>0.9519</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0384</v>
+        <v>-0.676</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4689</v>
+        <v>1.6279</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3553</v>
+        <v>-0.5063</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5349</v>
+        <v>-0.4369</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1796</v>
+        <v>-0.0694</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8731</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6433</v>
+        <v>-0.4877</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4567</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1866</v>
+        <v>-0.3882</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4037</v>
+        <v>-0.3846</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0137</v>
+        <v>0.0934</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3899</v>
+        <v>-0.478</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6059</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0059</v>
+        <v>0.0132</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1246</v>
+        <v>0.0365</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4208</v>
+        <v>-0.3959</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0574</v>
+        <v>-2.1927</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4782</v>
+        <v>1.7968</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4456</v>
+        <v>-3.5924</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1129</v>
+        <v>-1.7995</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5585</v>
+        <v>-1.7929</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9519</v>
+        <v>-3.3351</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.676</v>
+        <v>-2.3586</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6279</v>
+        <v>-0.9765</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5063</v>
+        <v>-0.2574</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4369</v>
+        <v>0.5591</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0694</v>
+        <v>-0.8164</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.702</v>
+        <v>0.3859</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3138</v>
+        <v>0.1829</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3882</v>
+        <v>0.203</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4599</v>
+        <v>0.9376</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4599</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7173</v>
+        <v>-0.707</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0187</v>
+        <v>-0.1259</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6986</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0039</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6217</v>
+        <v>0.632</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6054</v>
+        <v>0.4982</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0164</v>
+        <v>0.1338</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1675</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5814</v>
+        <v>-0.7704</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3644</v>
+        <v>0.4575</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7831</v>
+        <v>-1.228</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3795</v>
+        <v>0.3206</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2022</v>
+        <v>2.7315</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1773</v>
+        <v>-2.4109</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2611</v>
+        <v>1.1945</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6183999999999999</v>
+        <v>3.1808</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6427</v>
+        <v>-1.9864</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8816000000000001</v>
+        <v>-0.8739</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4162</v>
+        <v>-0.4494</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4654</v>
+        <v>-0.4245</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4568</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>-2.2893</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.7633</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.3849</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6746</v>
+        <v>0.3785</v>
       </c>
       <c r="V20" t="n">
+        <v>-0.8137</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.1675</v>
       </c>
-      <c r="W20" t="n">
-        <v>2.565</v>
-      </c>
       <c r="X20" t="n">
-        <v>-1.3975</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6062</v>
+        <v>-0.8837</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0289</v>
+        <v>-1.7215</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6351</v>
+        <v>0.8379</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3206</v>
+        <v>-1.3795</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7315</v>
+        <v>-0.2022</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4109</v>
+        <v>-1.1773</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1945</v>
+        <v>-2.2611</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1808</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9864</v>
+        <v>-1.6427</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8739</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4494</v>
+        <v>0.4162</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4245</v>
+        <v>0.4654</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0406</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07240000000000001</v>
+        <v>0.7852</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0438</v>
+        <v>0.0557</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0287</v>
+        <v>0.7294</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>2.565</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9813</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6064</v>
+        <v>-1.014</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2643</v>
+        <v>-1.4055</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6579</v>
+        <v>0.3915</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.5924</v>
+        <v>-2.451</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7995</v>
+        <v>-1.0981</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7929</v>
+        <v>-1.3528</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.3351</v>
+        <v>-2.8183</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3586</v>
+        <v>-1.4287</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9765</v>
+        <v>-1.3896</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2574</v>
+        <v>0.3674</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5591</v>
+        <v>0.3306</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8164</v>
+        <v>0.0367</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0812</v>
+        <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8246</v>
+        <v>0.0613</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8885999999999999</v>
+        <v>0.2453</v>
       </c>
       <c r="U22" t="n">
-        <v>0.064</v>
+        <v>-0.184</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9376</v>
+        <v>1.1675</v>
       </c>
       <c r="W22" t="n">
         <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6818</v>
+        <v>-1.9088</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0424</v>
+        <v>-2.471</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3606</v>
+        <v>0.5622</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6806</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5826</v>
+        <v>0.3555</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7887</v>
+        <v>0.3601</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2061</v>
+        <v>-0.0045</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,37 +2281,37 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.955700000000001</v>
+        <v>9.384400000000003</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7257000000000007</v>
+        <v>-0.7259000000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>8.6816</v>
+        <v>10.1104</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9808</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9179999999999999</v>
+        <v>0.9180000000000004</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.8986</v>
+        <v>-5.898599999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.039899999999999</v>
+        <v>-4.0399</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1036999999999998</v>
+        <v>0.1037000000000002</v>
       </c>
       <c r="L24" t="n">
         <v>-4.1436</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9409000000000003</v>
+        <v>-0.9408999999999998</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8144000000000003</v>
+        <v>0.8144</v>
       </c>
       <c r="O24" t="n">
         <v>-1.7552</v>
@@ -2326,13 +2326,13 @@
         <v>13.5276</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1218</v>
+        <v>4.5504</v>
       </c>
       <c r="T24" t="n">
-        <v>2.6221</v>
+        <v>2.6222</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4994</v>
+        <v>1.928300000000001</v>
       </c>
       <c r="V24" t="n">
         <v>8.7742</v>
